--- a/data/trans_orig/IP07A11-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP07A11-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2007 (tasa de respuesta: 99,6%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2007 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>524</t>
+          <t>522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4554</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,47 +747,47 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2843</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6438</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>2,33%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>20,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2843</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>712</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1958</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8897</t>
+          <t>8734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9448</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>74,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16453</t>
+          <t>16534</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25087</t>
+          <t>25043</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,81%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>28746</t>
+          <t>28632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39880</t>
+          <t>39565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,53%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10866</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>19596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21594</t>
+          <t>21861</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31758</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40969</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50857</t>
+          <t>50537</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,72%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64249</t>
+          <t>65844</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79632</t>
+          <t>80364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>64,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20203</t>
+          <t>19390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15183</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>19032</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33929</t>
+          <t>31795</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>633</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5679</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>3487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17390</t>
+          <t>17128</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23515</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16535</t>
+          <t>16672</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>19874</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>26706</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28848</t>
+          <t>29260</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>42119</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,38%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>14845</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3167</t>
+          <t>2635</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6467</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16667</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3987</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4520</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,91%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10674</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5681</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11254</t>
+          <t>10907</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22598</t>
+          <t>22632</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,13%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>21371</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30648</t>
+          <t>30980</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>17800</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27979</t>
+          <t>27778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>42597</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>56337</t>
+          <t>56242</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>9714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6818</t>
+          <t>6845</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>16851</t>
+          <t>16614</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>3831</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3192,7 +3192,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6815</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14319</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7757</t>
+          <t>8428</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>17004</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>28519</t>
+          <t>27723</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>65,4%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10030</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12008</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9196</t>
+          <t>9654</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19578</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>5638</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2760</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9783</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>24,02%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1932</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>8045</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1844</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>8333</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>5268</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>14313</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,29%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>12725</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>21104</t>
+          <t>21030</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>14926</t>
+          <t>15070</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23095</t>
+          <t>23094</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>30154</t>
+          <t>30186</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>41629</t>
+          <t>42756</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2664</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>9634</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10994</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17972</t>
+          <t>17364</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>29,89%</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4486,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3885</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3562</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15802</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>28284</t>
+          <t>27327</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>15482</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>27922</t>
+          <t>27624</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>34935</t>
+          <t>35206</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>52545</t>
+          <t>52462</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>44,05%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>31193</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>21453</t>
+          <t>21594</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>34276</t>
+          <t>33919</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,63%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,4%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>44238</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>61733</t>
+          <t>62130</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>52,17%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3955</t>
+          <t>4159</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>12511</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7466</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18375</t>
+          <t>17818</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>14271</t>
+          <t>13886</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>27802</t>
+          <t>26889</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>686</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -5506,12 +5506,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>19061</t>
+          <t>18743</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>31397</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5521,12 +5521,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>28583</t>
+          <t>28344</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>42321</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>51490</t>
+          <t>50879</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>70012</t>
+          <t>70004</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,88%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>33768</t>
+          <t>33480</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>47059</t>
+          <t>46713</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>21784</t>
+          <t>21557</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>34406</t>
+          <t>34466</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5669,12 +5669,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>58227</t>
+          <t>57587</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>78252</t>
+          <t>77399</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,83%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>14299</t>
+          <t>14497</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>12927</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>12174</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -5850,7 +5850,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3307</t>
+          <t>3668</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5865,7 +5865,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>4839</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>675</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6200</t>
+          <t>5650</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5963,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5998,7 +5998,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3861</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>95083</t>
+          <t>96092</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>122243</t>
+          <t>124437</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>123782</t>
+          <t>125182</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>153070</t>
+          <t>154451</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>228089</t>
+          <t>226530</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>267934</t>
+          <t>268509</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>141799</t>
+          <t>141077</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>170559</t>
+          <t>170483</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>44,18%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>145222</t>
+          <t>144566</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>173807</t>
+          <t>173229</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>293619</t>
+          <t>296817</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>335958</t>
+          <t>339033</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>41181</t>
+          <t>40593</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>62311</t>
+          <t>62198</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>33877</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>53772</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>81324</t>
+          <t>79959</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>109493</t>
+          <t>108915</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1175</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6582,7 +6582,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>3874</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>12982</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2608</t>
+          <t>2323</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3409</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6715,7 +6715,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4296</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -6911,7 +6911,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2012 (tasa de respuesta: 98,23%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2012 (tasa de respuesta: 98,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15001</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>22029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7121,12 +7121,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>64,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7141,12 +7141,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16029</t>
+          <t>16392</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24803</t>
+          <t>25077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7156,12 +7156,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>53,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7176,12 +7176,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34728</t>
+          <t>34962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45084</t>
+          <t>45438</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7191,12 +7191,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -7219,12 +7219,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7234,12 +7234,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7254,12 +7254,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12973</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7269,12 +7269,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7289,12 +7289,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17350</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7304,12 +7304,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>29,91%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>547</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4976</t>
+          <t>4744</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1218</t>
+          <t>1129</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7298</t>
+          <t>7252</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28401</t>
+          <t>28463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7823,12 +7823,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36505</t>
+          <t>36626</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46464</t>
+          <t>45887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7838,12 +7838,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7858,12 +7858,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67697</t>
+          <t>68713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82110</t>
+          <t>82726</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7873,12 +7873,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -7901,12 +7901,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8221</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>17798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7936,12 +7936,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11379</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7971,12 +7971,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13790</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26536</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,3%</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4671</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1205</t>
+          <t>621</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8293</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>9345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8167,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8202,7 +8202,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3985</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8217,7 +8217,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8315,7 +8315,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8330,7 +8330,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -8470,12 +8470,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11780</t>
+          <t>11940</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>19934</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8485,12 +8485,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>17919</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23822</t>
+          <t>23507</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35949</t>
+          <t>36001</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -8583,12 +8583,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13741</t>
+          <t>13581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8618,12 +8618,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12445</t>
+          <t>12296</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21380</t>
+          <t>21673</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32272</t>
+          <t>32467</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>56,67%</t>
         </is>
       </c>
     </row>
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4967</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -9152,12 +9152,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12758</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23328</t>
+          <t>22716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>59,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9187,12 +9187,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14913</t>
+          <t>15357</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24183</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9202,12 +9202,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30737</t>
+          <t>30538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45062</t>
+          <t>45414</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9237,12 +9237,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,24%</t>
         </is>
       </c>
     </row>
@@ -9265,12 +9265,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18912</t>
+          <t>19080</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9300,12 +9300,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7945</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9315,12 +9315,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9335,12 +9335,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19284</t>
+          <t>19388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>32688</t>
+          <t>32999</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9350,12 +9350,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>45,22%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2427</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9413,12 +9413,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5484</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3998</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>3169</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>5282</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -9834,12 +9834,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10607</t>
+          <t>11105</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17968</t>
+          <t>18182</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9849,82 +9849,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>88,22%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>17196</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>13450</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>19504</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>82,66%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>64,65%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>93,75%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>32300</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>26435</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>36103</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>77,99%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>63,83%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>87,18%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>17196</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>13503</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>19453</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>82,66%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>64,91%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>93,5%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>32300</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>27044</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>36249</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>77,99%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>65,3%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>87,53%</t>
         </is>
       </c>
     </row>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2240</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9294</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>13812</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10065,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10080,7 +10080,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10135,7 +10135,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3476</t>
+          <t>3460</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10150,7 +10150,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -10516,12 +10516,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>12007</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>21184</t>
+          <t>21407</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>69,53%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>8611</t>
+          <t>8450</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17048</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>23356</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>35805</t>
+          <t>35450</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>62,5%</t>
         </is>
       </c>
     </row>
@@ -10629,12 +10629,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7798</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16726</t>
+          <t>16678</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10644,12 +10644,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10664,12 +10664,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10679,12 +10679,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10699,12 +10699,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>17187</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>30190</t>
+          <t>29578</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10797,7 +10797,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8595</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11023,7 +11023,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>3831</t>
+          <t>3495</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,16%</t>
         </is>
       </c>
     </row>
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>21058</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>33612</t>
+          <t>33533</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11213,12 +11213,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11233,12 +11233,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>21657</t>
+          <t>21281</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>34018</t>
+          <t>33274</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11248,12 +11248,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>61,47%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11268,12 +11268,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>46175</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>63473</t>
+          <t>62867</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11283,12 +11283,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -11311,12 +11311,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20033</t>
+          <t>19847</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>32854</t>
+          <t>32214</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11326,12 +11326,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>17477</t>
+          <t>17457</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>29853</t>
+          <t>29392</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11381,12 +11381,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>40611</t>
+          <t>41245</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>58522</t>
+          <t>58199</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,97%</t>
         </is>
       </c>
     </row>
@@ -11424,12 +11424,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>693</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11439,12 +11439,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1258</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7601</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11494,12 +11494,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2692</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>10025</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -11542,7 +11542,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>2728</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11577,7 +11577,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>618</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>5730</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11627,7 +11627,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -11880,12 +11880,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>20424</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>34314</t>
+          <t>33606</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11895,12 +11895,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>33221</t>
+          <t>33930</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11930,12 +11930,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>43590</t>
+          <t>43420</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>63053</t>
+          <t>62792</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,46%</t>
         </is>
       </c>
     </row>
@@ -11993,12 +11993,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>33788</t>
+          <t>32976</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>48482</t>
+          <t>47998</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12008,12 +12008,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>34741</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>48801</t>
+          <t>48368</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,81%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>71985</t>
+          <t>72828</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>92636</t>
+          <t>92310</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12078,12 +12078,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>17957</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5174</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14340</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>14876</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>28317</t>
+          <t>29012</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -12224,7 +12224,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12239,7 +12239,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>581</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5581</t>
+          <t>4690</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>6468</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>158844</t>
+          <t>157065</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>187235</t>
+          <t>186000</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,68%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>166008</t>
+          <t>165792</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>195146</t>
+          <t>194485</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>332317</t>
+          <t>333438</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>373725</t>
+          <t>374374</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,14%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>107480</t>
+          <t>109631</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>137045</t>
+          <t>137987</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>109603</t>
+          <t>110293</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>138011</t>
+          <t>139073</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>225573</t>
+          <t>226943</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>265749</t>
+          <t>266584</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>17927</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>34330</t>
+          <t>33911</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>15609</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>30848</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>37671</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>59562</t>
+          <t>58208</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>626</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>5823</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12921,7 +12921,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>8633</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3472</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4513</t>
+          <t>4674</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13089,7 +13089,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -13285,7 +13285,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haber podido estar al aire libre en 2016 (tasa de respuesta: 98,92%)</t>
+          <t>Menores según la frecuencia de haber podido estar al aire libre, percibida por el adulto en 2016 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19360</t>
+          <t>19487</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26183</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13495,12 +13495,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13515,12 +13515,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14834</t>
+          <t>14814</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>23127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13530,12 +13530,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,36%</t>
+          <t>52,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13550,12 +13550,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>36696</t>
+          <t>35975</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47494</t>
+          <t>47137</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13565,12 +13565,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -13593,12 +13593,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13608,12 +13608,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13628,12 +13628,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9672</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13643,12 +13643,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3507</t>
+          <t>3895</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12010</t>
+          <t>12685</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13678,12 +13678,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -13706,12 +13706,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8110</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13721,12 +13721,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13741,12 +13741,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6956</t>
+          <t>6740</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13776,12 +13776,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4398</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13791,12 +13791,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -13859,7 +13859,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13909,7 +13909,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>29550</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14177,12 +14177,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14197,12 +14197,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>25306</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37756</t>
+          <t>37747</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14212,12 +14212,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14232,12 +14232,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>47227</t>
+          <t>46732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63629</t>
+          <t>63559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14247,12 +14247,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -14275,12 +14275,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15915</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28347</t>
+          <t>27567</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -14290,12 +14290,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>52,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14310,12 +14310,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17871</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30064</t>
+          <t>30252</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14325,12 +14325,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14345,12 +14345,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37576</t>
+          <t>37335</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53913</t>
+          <t>53557</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14360,12 +14360,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,33%</t>
         </is>
       </c>
     </row>
@@ -14388,12 +14388,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13253</t>
+          <t>12333</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14403,12 +14403,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4931</t>
+          <t>4955</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15020</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14473,12 +14473,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,5%</t>
         </is>
       </c>
     </row>
@@ -14541,7 +14541,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3327</t>
+          <t>3658</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3623</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -14844,12 +14844,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13108</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23910</t>
+          <t>24014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -14859,12 +14859,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -14879,12 +14879,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9918</t>
+          <t>9486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19621</t>
+          <t>18990</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -14894,12 +14894,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -14914,12 +14914,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>40935</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -14929,12 +14929,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,94%</t>
+          <t>58,85%</t>
         </is>
       </c>
     </row>
@@ -14957,12 +14957,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17859</t>
+          <t>17764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -14972,12 +14972,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -14992,12 +14992,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17870</t>
+          <t>17729</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15007,12 +15007,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,98%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15027,12 +15027,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17587</t>
+          <t>17872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31388</t>
+          <t>31463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15042,12 +15042,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -15070,12 +15070,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15085,12 +15085,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15105,12 +15105,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3541</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11749</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15120,12 +15120,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15140,12 +15140,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18107</t>
+          <t>17515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15155,12 +15155,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -15526,12 +15526,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21359</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15541,12 +15541,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15561,12 +15561,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28360</t>
+          <t>28244</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>37975</t>
+          <t>37865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15576,12 +15576,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,51%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52831</t>
+          <t>53199</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>66998</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15611,12 +15611,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>80,49%</t>
         </is>
       </c>
     </row>
@@ -15639,12 +15639,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12142</t>
+          <t>12289</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15654,12 +15654,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15674,12 +15674,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>8417</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15689,12 +15689,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>6547</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17319</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -15752,12 +15752,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1232</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15767,12 +15767,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>772</t>
+          <t>778</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15802,12 +15802,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15822,12 +15822,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15837,12 +15837,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>595</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15880,12 +15880,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15900,12 +15900,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>6551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15915,12 +15915,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -15983,7 +15983,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16018,7 +16018,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16053,7 +16053,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6966</t>
+          <t>5919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -16208,12 +16208,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10131</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16223,12 +16223,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16243,12 +16243,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>816</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6286</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16258,12 +16258,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16278,12 +16278,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5120</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>14080</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16293,12 +16293,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -16321,12 +16321,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>13355</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16336,12 +16336,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,3%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16356,12 +16356,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14732</t>
+          <t>14860</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22142</t>
+          <t>22398</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16391,12 +16391,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>22764</t>
+          <t>23184</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>33367</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16406,12 +16406,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>51,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>74,41%</t>
         </is>
       </c>
     </row>
@@ -16434,12 +16434,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8530</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16469,12 +16469,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7775</t>
+          <t>7980</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16484,12 +16484,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3813</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>12185</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16519,12 +16519,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -16552,7 +16552,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -16890,12 +16890,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>13664</t>
+          <t>14147</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>22656</t>
+          <t>23363</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -16905,12 +16905,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -16925,12 +16925,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>14204</t>
+          <t>14316</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>23741</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16940,12 +16940,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>31794</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>44043</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16975,12 +16975,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>73,01%</t>
         </is>
       </c>
     </row>
@@ -17003,12 +17003,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12935</t>
+          <t>12811</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17038,12 +17038,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14425</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17053,12 +17053,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>11884</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>25014</t>
+          <t>23911</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -17116,12 +17116,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17131,47 +17131,47 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>19,11%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>3020</t>
-        </is>
-      </c>
-      <c r="N36" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>749</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -17234,7 +17234,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5202</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17249,7 +17249,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17269,7 +17269,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3649</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17284,7 +17284,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>649</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>7280</t>
+          <t>6968</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -17572,12 +17572,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>23435</t>
+          <t>23589</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>37301</t>
+          <t>36780</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -17587,12 +17587,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,21%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>24795</t>
+          <t>25105</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38956</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17622,12 +17622,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>51914</t>
+          <t>52783</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>71790</t>
+          <t>71137</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17657,12 +17657,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,79%</t>
         </is>
       </c>
     </row>
@@ -17685,12 +17685,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>20020</t>
+          <t>20585</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>34115</t>
+          <t>33687</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -17700,12 +17700,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -17720,12 +17720,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>23875</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>37926</t>
+          <t>37054</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -17735,12 +17735,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,72%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -17755,12 +17755,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>48721</t>
+          <t>47858</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>67390</t>
+          <t>66375</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -17770,12 +17770,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>50,19%</t>
         </is>
       </c>
     </row>
@@ -17798,12 +17798,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>5837</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17813,12 +17813,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>706</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>18420</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -17916,7 +17916,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17986,7 +17986,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -18001,7 +18001,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -18254,12 +18254,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>21385</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>35216</t>
+          <t>35477</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -18269,12 +18269,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>44,08%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -18289,12 +18289,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>27203</t>
+          <t>27719</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>41596</t>
+          <t>41703</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18304,12 +18304,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18324,12 +18324,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>52688</t>
+          <t>52563</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>72806</t>
+          <t>72140</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18339,12 +18339,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,94%</t>
         </is>
       </c>
     </row>
@@ -18367,12 +18367,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>32547</t>
+          <t>32384</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>48015</t>
+          <t>46984</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -18382,12 +18382,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>60,1%</t>
+          <t>58,81%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -18402,12 +18402,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>25494</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>39706</t>
+          <t>39955</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -18417,12 +18417,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -18437,12 +18437,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>62307</t>
+          <t>62220</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>82755</t>
+          <t>82977</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18452,12 +18452,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,84%</t>
         </is>
       </c>
     </row>
@@ -18480,12 +18480,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>6091</t>
+          <t>5863</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>15585</t>
+          <t>15332</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18495,12 +18495,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>14631</t>
+          <t>14905</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>13275</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>26985</t>
+          <t>27267</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -18598,7 +18598,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18613,7 +18613,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18668,7 +18668,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4519</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18683,7 +18683,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -18711,7 +18711,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>3736</t>
+          <t>3705</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18726,7 +18726,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18746,7 +18746,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18761,7 +18761,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18781,7 +18781,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3885</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18796,7 +18796,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>158193</t>
+          <t>160545</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>189781</t>
+          <t>190763</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>170950</t>
+          <t>173250</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>204750</t>
+          <t>202594</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,06%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>341192</t>
+          <t>340281</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>382552</t>
+          <t>384763</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>112452</t>
+          <t>113727</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>142691</t>
+          <t>143683</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>122087</t>
+          <t>122059</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>152413</t>
+          <t>151755</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,47 +19099,47 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
+          <t>33,78%</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr">
+        <is>
+          <t>264724</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>242439</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>285390</t>
+        </is>
+      </c>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>36,89%</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
           <t>33,79%</t>
         </is>
       </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>42,18%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>264724</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>243973</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>285832</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>36,89%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>34,0%</t>
-        </is>
-      </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,77%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>36812</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>56644</t>
+          <t>57601</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>23467</t>
+          <t>21977</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>40467</t>
+          <t>39776</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>63395</t>
+          <t>62416</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>90630</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,7%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>12027</t>
+          <t>12156</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1451</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>8404</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>6191</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>16343</t>
+          <t>17096</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19408,7 +19408,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19428,7 +19428,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4336</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19443,7 +19443,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>748</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7901</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19478,7 +19478,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
